--- a/04_DESIGN_TABLES/DesignTable_6505_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6505_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,17 +2619,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6505-12-10</t>
+          <t>6505-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65241</v>
+        <v>0.64952</v>
       </c>
       <c r="D13" t="n">
-        <v>1.13</v>
+        <v>1.125</v>
       </c>
       <c r="E13" t="n">
         <v>0.51241</v>
@@ -2659,103 +2659,103 @@
         <v>0.45527</v>
       </c>
       <c r="N13" t="n">
-        <v>0.985</v>
+        <v>0.885</v>
       </c>
       <c r="O13" t="n">
-        <v>0.347</v>
+        <v>0.292</v>
       </c>
       <c r="P13" t="n">
-        <v>0.944</v>
+        <v>0.827</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4758</v>
+        <v>0.4108</v>
       </c>
       <c r="R13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4988</v>
+        <v>0.4361</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="U13" t="n">
-        <v>0.57735</v>
+        <v>0.50518</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="W13" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="X13" t="n">
-        <v>0.404</v>
+        <v>0.3283</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4475</v>
+        <v>0.3925</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7794</v>
+        <v>0.6723</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.394</v>
+        <v>0.34</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3375</v>
+        <v>0.2825</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.4364</v>
+        <v>0.3567</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.9925</v>
+        <v>0.9775</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.48</v>
+        <v>0.391</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.7275</v>
+        <v>0.6925</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.9925</v>
+        <v>0.9775</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.235</v>
+        <v>1.205</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>6505-12-10</t>
+          <t>6505-12-08</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -2780,23 +2780,28 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (left out of batch 15, staged): L15@DRIVE: OMi Items row 2021 Overall Length = 2.09; L16@DRIVE: OMi Items row 2021 L 1 Size = 1.67; CHEX@HEX: OMi Items row 2021 Hex Flat = 1.125; C3HEX@HEX: OMi Items row 2021 Nut Hex 1 = 0.875; D1@BORE: OMi Items row 2021 Side 1 ID = 0.719; D@BORE: OMi Items row 2021 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 3/4-14 -&gt; 1.05 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi Overall Length = L15 (pipe tip to the swivel-nut face), L 1 = L16 (pipe tip to the seat), Hex Flat = body hex CHEX, Nut Hex 1 = swivel nut hex C3HEX, Side 1 / 2 ID = pipe / swivel bore - pairing READ from the built 6505-12-12 row (OMi 2.28 / 1.72 vs its Air-Way L15 2.26 / L16 1.70; the 2026-09-25 audit marks the 6505 length mapping "uncertain") - ASSUMPTION | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 2021 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p018-t01: TUBE O.D. 1/2, A NPTF 3/4-14, B SAE 37Deg 3/4-16, A DRILL 0.609, B DRILL 0.391, L LGTH 1.67, L5 LGTH 2.09, C1 HEX 0.875, C HEX 1.125</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>6505-12-10</t>
+          <t>6505-12-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6505-12-12</t>
+          <t>6505-12-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="C14" t="n">
         <v>0.65241</v>
@@ -2832,103 +2837,103 @@
         <v>0.45527</v>
       </c>
       <c r="N14" t="n">
-        <v>1.089</v>
+        <v>0.985</v>
       </c>
       <c r="O14" t="n">
-        <v>0.417</v>
+        <v>0.347</v>
       </c>
       <c r="P14" t="n">
-        <v>1.047</v>
+        <v>0.944</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5928</v>
+        <v>0.4758</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6237</v>
+        <v>0.4988</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="V14" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="W14" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4472</v>
+        <v>0.404</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.549</v>
+        <v>0.4475</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.8623</v>
+        <v>0.7794</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.481</v>
+        <v>0.394</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4225</v>
+        <v>0.3375</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.97228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.4851</v>
+        <v>0.4364</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.48614</v>
+        <v>0.39884</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.9605</v>
+        <v>0.9925</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.7395</v>
+        <v>0.7275</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.9605</v>
+        <v>0.9925</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.171</v>
+        <v>1.235</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.5998</v>
+        <v>0.5265</v>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>6505-12-12</t>
+          <t>6505-12-10</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
@@ -2943,7 +2948,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -2956,31 +2961,26 @@
           <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.61 used through</t>
-        </is>
-      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>6505-12-12</t>
+          <t>6505-12-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6505-12-16</t>
+          <t>6505-12-12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="C15" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D15" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E15" t="n">
         <v>0.51241</v>
@@ -3010,103 +3010,103 @@
         <v>0.45527</v>
       </c>
       <c r="N15" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="P15" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="R15" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="U15" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="W15" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.719</v>
+        <v>0.61</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.8025</v>
+        <v>0.7395</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.185</v>
+        <v>1.171</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>6505-12-16</t>
+          <t>6505-12-12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -3131,155 +3131,160 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.61 used through</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>6505-12-16</t>
+          <t>6505-12-12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6505-16-12</t>
+          <t>6505-12-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="C16" t="n">
-        <v>0.79386</v>
+        <v>0.79674</v>
       </c>
       <c r="D16" t="n">
-        <v>1.375</v>
+        <v>1.38</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G16" t="n">
         <v>1.7899</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M16" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N16" t="n">
-        <v>1.089</v>
+        <v>1.175</v>
       </c>
       <c r="O16" t="n">
-        <v>0.417</v>
+        <v>0.5485</v>
       </c>
       <c r="P16" t="n">
-        <v>1.047</v>
+        <v>1.139</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5928</v>
+        <v>0.727</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6237</v>
+        <v>0.749</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5998</v>
+        <v>0.6564</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.86603</v>
       </c>
       <c r="V16" t="n">
-        <v>0.53125</v>
+        <v>0.65625</v>
       </c>
       <c r="W16" t="n">
-        <v>0.48614</v>
+        <v>0.61114</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4472</v>
+        <v>0.4873</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.549</v>
+        <v>0.665</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.8623</v>
+        <v>0.9544</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.481</v>
+        <v>0.604</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4225</v>
+        <v>0.5475</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.97228</v>
+        <v>1.22228</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.4851</v>
+        <v>0.5252</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.48614</v>
+        <v>0.61114</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.53125</v>
+        <v>0.65625</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.1655</v>
+        <v>0.9675</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.609</v>
+        <v>0.719</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.8025</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.1655</v>
+        <v>0.9675</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.391</v>
+        <v>1.185</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5998</v>
+        <v>0.6564</v>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>6505-16-12</t>
+          <t>6505-12-16</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>Male Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF x 1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>Male Pipe x Female JIC Swivel Connector, 3/4-14 NPTF x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
@@ -3289,12 +3294,12 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -3304,34 +3309,29 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): dimensions from OMi WebsitePartsInfo2026.xlsx alone (one source; OMi = Brennan data, evidence 2026-09-26): L15@DRIVE Items!L2025 Overall Length = 2.48, L16@DRIVE Items!P2025 L 1 Size = 1.91 (OMi Overall Length = pipe tip to swivel-nut face, L 1 = pipe tip to stem nose / seat: settled by the Brennan TFA catalog p18 6505 drawing letters L5 / L, Q-B-SWSTR), CHEX@HEX Items!R2025 Hex Flat = 1.375, C3HEX@HEX Items!V2025 Nut Hex 1 = 1.250, D1@BORE Items!S2025 Side 1 ID = 0.938, D@BORE Items!X2025 Side 2 ID = 0.609 (table had empty: no Air-Way row); threads OMi Items!U2025 "1 11-1/2 NPTF" / AA2025 "1-1/16-12 UN" -&gt; THDMAJ_A@DRIVE 1.315 (ASME B1.20.1 pipe OD), THDMAJ_B@DRIVE 1.0625 (thread major); TubeOD = OMi Items!Z2025 Side 2 Size 3/4 [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | batch 15, 2026-10-02 (staged, not shipped): built from OMi alone (ASSUMED); not in the Brennan TFA catalog (p18 6505 lists no 6505-16-12): OMi values only</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>6505-16-12</t>
+          <t>6505-12-16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6505-16-16</t>
+          <t>6505-16-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79674</v>
+        <v>0.79386</v>
       </c>
       <c r="D17" t="n">
-        <v>1.38</v>
+        <v>1.375</v>
       </c>
       <c r="E17" t="n">
         <v>0.6415999999999999</v>
@@ -3361,103 +3361,103 @@
         <v>0.57203</v>
       </c>
       <c r="N17" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="P17" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="R17" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="U17" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="W17" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AF17" t="n">
         <v>0.08333</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.84</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.1625</v>
+        <v>1.1655</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.84</v>
+        <v>0.609</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.8075</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.1625</v>
+        <v>1.1655</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.385</v>
+        <v>1.391</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>6505-16-16</t>
+          <t>6505-16-12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>Male Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>Male Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -3482,34 +3482,34 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; batch 15, 2026-10-02 (staged, not shipped): dimensions from OMi WebsitePartsInfo2026.xlsx alone (one source; OMi = Brennan data, evidence 2026-09-26): L15@DRIVE Items!L2025 Overall Length = 2.48, L16@DRIVE Items!P2025 L 1 Size = 1.91 (OMi Overall Length = pipe tip to swivel-nut face, L 1 = pipe tip to stem nose / seat: settled by the Brennan TFA catalog p18 6505 drawing letters L5 / L, Q-B-SWSTR), CHEX@HEX Items!R2025 Hex Flat = 1.375, C3HEX@HEX Items!V2025 Nut Hex 1 = 1.250, D1@BORE Items!S2025 Side 1 ID = 0.938, D@BORE Items!X2025 Side 2 ID = 0.609 (table had empty: no Air-Way row); threads OMi Items!U2025 "1 11-1/2 NPTF" / AA2025 "1-1/16-12 UN" -&gt; THDMAJ_A@DRIVE 1.315 (ASME B1.20.1 pipe OD), THDMAJ_B@DRIVE 1.0625 (thread major); TubeOD = OMi Items!Z2025 Side 2 Size 3/4 [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.84 used through</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | batch 15, 2026-10-02 (staged, not shipped): built from OMi alone (ASSUMED); not in the Brennan TFA catalog (p18 6505 lists no 6505-16-12): OMi values only</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>6505-16-16</t>
+          <t>6505-16-12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6505-16-20</t>
+          <t>6505-16-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="C18" t="n">
-        <v>0.97572</v>
+        <v>0.79674</v>
       </c>
       <c r="D18" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="E18" t="n">
         <v>0.6415999999999999</v>
@@ -3539,103 +3539,103 @@
         <v>0.57203</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>1.175</v>
       </c>
       <c r="O18" t="n">
-        <v>0.68</v>
+        <v>0.5485</v>
       </c>
       <c r="P18" t="n">
-        <v>1.145</v>
+        <v>1.139</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.949</v>
+        <v>0.727</v>
       </c>
       <c r="R18" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9889</v>
+        <v>0.749</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5375</v>
+        <v>0.6564</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1547</v>
+        <v>0.86603</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="W18" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4345</v>
+        <v>0.4873</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.88</v>
+        <v>0.665</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.9556</v>
+        <v>0.9544</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.766</v>
+        <v>0.604</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.7025</v>
+        <v>0.5475</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53478</v>
+        <v>1.22228</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.4724</v>
+        <v>0.5252</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08333</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.155</v>
+        <v>1.1625</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.845</v>
+        <v>0.8075</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.155</v>
+        <v>1.1625</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.37</v>
+        <v>1.385</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.5375</v>
+        <v>0.6564</v>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6505-16-20</t>
+          <t>6505-16-16</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>Male Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>Male Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -3663,20 +3663,25 @@
           <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.84 used through</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>6505-16-20</t>
+          <t>6505-16-16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6505-20-20</t>
+          <t>6505-16-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="C19" t="n">
         <v>0.97572</v>
@@ -3685,31 +3690,31 @@
         <v>1.69</v>
       </c>
       <c r="E19" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G19" t="n">
         <v>1.7899</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K19" t="n">
         <v>0.08696</v>
       </c>
       <c r="L19" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N19" t="n">
         <v>1.26</v>
@@ -3775,13 +3780,13 @@
         <v>0.8125</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.185</v>
+        <v>1.155</v>
       </c>
       <c r="AL19" t="n">
         <v>1.08</v>
@@ -3790,10 +3795,10 @@
         <v>0.845</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.185</v>
+        <v>1.155</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AP19" t="n">
         <v>2</v>
@@ -3803,45 +3808,218 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>6505-16-20</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Male Pipe x Female JIC Swivel Connector, 1-11 1/2 NPTF x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>6505-16-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>6505-20-20</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
+      <c r="B20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.97572</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>6505-20-20</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
         <is>
           <t>Male Pipe x Female JIC Swivel Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>6505</t>
         </is>
       </c>
-      <c r="AU19" t="inlineStr">
+      <c r="AU20" t="inlineStr">
         <is>
           <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AV19" t="inlineStr">
+      <c r="AV20" t="inlineStr">
         <is>
           <t>1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 1.08 used through</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>6505-20-20</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6505_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6505_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="C2" t="n">
         <v>0.50807</v>
@@ -779,25 +779,25 @@
         <v>0.375</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.39</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8825</v>
+        <v>0.9225</v>
       </c>
       <c r="AL2" t="n">
         <v>0.39</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5975</v>
+        <v>0.6375</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8825</v>
+        <v>0.9225</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.015</v>
+        <v>1.095</v>
       </c>
       <c r="AP2" t="n">
         <v>0.88</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2018 = 1.98 (table had 1.9) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2018 = 1.56 (table had 1.48) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.39 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.9 -&gt; OMi 1.98 (Items!L2018, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.56 (Items!P2018, M032) | End A bore not printed by Air-Way (---): D 0.39 used through</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="C3" t="n">
         <v>0.28868</v>
@@ -936,7 +936,7 @@
         <v>0.1845</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="AC3" t="n">
         <v>0.145</v>
@@ -957,13 +957,13 @@
         <v>0.21875</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5175</v>
+        <v>0.5275</v>
       </c>
       <c r="AL3" t="n">
         <v>0.17</v>
@@ -972,10 +972,10 @@
         <v>0.4825</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.5175</v>
+        <v>0.5275</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.655</v>
+        <v>0.675</v>
       </c>
       <c r="AP3" t="n">
         <v>0.5600000000000001</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2009 = 1.36 (table had 1.34) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2009 = 1.01 (table had 1) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.17 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.34 -&gt; OMi 1.36 (Items!L2009, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1 -&gt; OMi 1.01 (Items!P2009, M032) | End A bore not printed by Air-Way (---): D 0.17 used through</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="C4" t="n">
         <v>0.32332</v>
@@ -1114,7 +1114,7 @@
         <v>0.1845</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="AC4" t="n">
         <v>0.145</v>
@@ -1135,25 +1135,25 @@
         <v>0.21875</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7025</v>
+        <v>0.7175</v>
       </c>
       <c r="AL4" t="n">
         <v>0.17</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.4875</v>
+        <v>0.4925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7025</v>
+        <v>0.7175</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.845</v>
+        <v>0.875</v>
       </c>
       <c r="AP4" t="n">
         <v>0.5600000000000001</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2011 = 1.56 (table had 1.53) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2011 = 1.21 (table had 1.19) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.17 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.53 -&gt; OMi 1.56 (Items!L2011, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.19 -&gt; OMi 1.21 (Items!P2011, M032) | End A bore not printed by Air-Way (---): D 0.17 used through</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="C5" t="n">
         <v>0.32332</v>
@@ -1292,7 +1292,7 @@
         <v>0.218</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AC5" t="n">
         <v>0.175</v>
@@ -1313,25 +1313,25 @@
         <v>0.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.722</v>
+        <v>0.727</v>
       </c>
       <c r="AL5" t="n">
         <v>0.23</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.538</v>
+        <v>0.533</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.722</v>
+        <v>0.727</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.884</v>
+        <v>0.894</v>
       </c>
       <c r="AP5" t="n">
         <v>0.63</v>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2012 = 1.64 (table had 1.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.23 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.63 -&gt; OMi 1.64 (Items!L2012, M031) | End A bore not printed by Air-Way (---): D 0.23 used through</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="C6" t="n">
         <v>0.32332</v>
@@ -1491,25 +1491,25 @@
         <v>0.28125</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7275</v>
       </c>
       <c r="AL6" t="n">
         <v>0.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5925</v>
+        <v>0.5725</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7275</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="AP6" t="n">
         <v>0.6899999999999999</v>
@@ -1549,7 +1549,12 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2013 = 1.68 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2013 = 1.30 (table had 1.34) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.68 (Items!L2013, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.30 (Items!P2013, M032)</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1743,7 +1748,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="C8" t="n">
         <v>0.43301</v>
@@ -1842,25 +1847,25 @@
         <v>0.28125</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="AL8" t="n">
         <v>0.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5925</v>
+        <v>0.5525</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.855</v>
       </c>
       <c r="AP8" t="n">
         <v>0.6899999999999999</v>
@@ -1900,12 +1905,12 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2015 = 1.64 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2015 = 1.26 (table had 1.34) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.3 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.64 (Items!L2015, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.26 (Items!P2015, M032) | End A bore not printed by Air-Way (---): D 0.3 used through</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2099,7 +2104,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="C10" t="n">
         <v>0.50807</v>
@@ -2177,7 +2182,7 @@
         <v>0.246</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AC10" t="n">
         <v>0.215</v>
@@ -2198,25 +2203,25 @@
         <v>0.28125</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.53</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.9125</v>
+        <v>0.9225</v>
       </c>
       <c r="AL10" t="n">
         <v>0.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5675</v>
+        <v>0.5875</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.9125</v>
+        <v>0.9225</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.075</v>
+        <v>1.095</v>
       </c>
       <c r="AP10" t="n">
         <v>0.6899999999999999</v>
@@ -2256,7 +2261,12 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2017 = 1.88 (table had 1.86) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2017 = 1.51 (table had 1.48) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.86 -&gt; OMi 1.88 (Items!L2017, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.51 (Items!P2017, M032)</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2272,7 +2282,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="C11" t="n">
         <v>0.57735</v>
@@ -2371,25 +2381,25 @@
         <v>0.4375</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.48</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.0225</v>
+        <v>0.9325</v>
       </c>
       <c r="AL11" t="n">
         <v>0.48</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.7575</v>
+        <v>0.6675</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.0225</v>
+        <v>0.9325</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.295</v>
+        <v>1.115</v>
       </c>
       <c r="AP11" t="n">
         <v>1</v>
@@ -2429,12 +2439,12 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2019 = 2.10 (table had 2.28) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2019 = 1.60 (table had 1.78) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.48 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.28 -&gt; OMi 2.10 (Items!L2019, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.78 -&gt; OMi 1.60 (Items!P2019, M032) | End A bore not printed by Air-Way (---): D 0.48 used through</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -2450,7 +2460,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="C12" t="n">
         <v>0.57735</v>
@@ -2549,25 +2559,25 @@
         <v>0.53125</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.53</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.9605</v>
+        <v>0.9005</v>
       </c>
       <c r="AL12" t="n">
         <v>0.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.7395</v>
+        <v>0.6795</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.9605</v>
+        <v>0.9005</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.171</v>
+        <v>1.051</v>
       </c>
       <c r="AP12" t="n">
         <v>1.25</v>
@@ -2607,7 +2617,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2020 = 2.14 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2020 = 1.58 (table had 1.7) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.14 (Items!L2020, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.58 (Items!P2020, M032)</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -2801,7 +2816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="C14" t="n">
         <v>0.65241</v>
@@ -2879,7 +2894,7 @@
         <v>0.394</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AC14" t="n">
         <v>0.3375</v>
@@ -2900,25 +2915,25 @@
         <v>0.4375</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.72</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.9925</v>
+        <v>0.9875</v>
       </c>
       <c r="AL14" t="n">
         <v>0.48</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.7275</v>
+        <v>0.7125</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.9925</v>
+        <v>0.9875</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.235</v>
+        <v>1.225</v>
       </c>
       <c r="AP14" t="n">
         <v>1</v>
@@ -2958,7 +2973,12 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2022 = 2.21 (table had 2.22) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2022 = 1.70 (table had 1.72) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.22 -&gt; OMi 2.21 (Items!L2022, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.72 -&gt; OMi 1.70 (Items!P2022, M032)</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -2974,7 +2994,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="C15" t="n">
         <v>0.65241</v>
@@ -3073,25 +3093,25 @@
         <v>0.53125</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.61</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.9605</v>
+        <v>0.9705</v>
       </c>
       <c r="AL15" t="n">
         <v>0.61</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.7395</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.9605</v>
+        <v>0.9705</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.171</v>
+        <v>1.191</v>
       </c>
       <c r="AP15" t="n">
         <v>1.25</v>
@@ -3131,12 +3151,12 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2023 = 2.28 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2023 = 1.72 (table had 1.7) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.61 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.28 (Items!L2023, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.72 (Items!P2023, M032) | End A bore not printed by Air-Way (---): D 0.61 used through</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -3152,7 +3172,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="C16" t="n">
         <v>0.79674</v>
@@ -3251,25 +3271,25 @@
         <v>0.65625</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AJ16" t="n">
         <v>0.72</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.9675</v>
+        <v>0.9775</v>
       </c>
       <c r="AL16" t="n">
         <v>0.719</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.8025</v>
+        <v>0.8125</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.9675</v>
+        <v>0.9775</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.185</v>
+        <v>1.205</v>
       </c>
       <c r="AP16" t="n">
         <v>1.5</v>
@@ -3309,7 +3329,12 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2024 = 2.38 (table had 2.36) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2024 = 1.79 (table had 1.77) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.36 -&gt; OMi 2.38 (Items!L2024, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.77 -&gt; OMi 1.79 (Items!P2024, M032)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -3655,7 +3680,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -3665,7 +3690,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.84 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L15@DRIVE=2.56~2.56; L16@DRIVE=1.97~1.97; CHEX@HEX=1.38~1.375; C3HEX@HEX=1.5~1.500; D@BORE=0.84~0.844 | End A bore not printed by Air-Way (---): D 0.84 used through</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -3854,7 +3879,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="C20" t="n">
         <v>0.97572</v>
@@ -3953,25 +3978,25 @@
         <v>0.8125</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.08</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.185</v>
+        <v>1.275</v>
       </c>
       <c r="AL20" t="n">
         <v>1.08</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.845</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.185</v>
+        <v>1.275</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AP20" t="n">
         <v>2</v>
@@ -4011,17 +4036,373 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2028 = 2.84 (table had 2.66) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2028 = 2.21 (table had 2.03) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.66 -&gt; OMi 2.84 (Items!L2028, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 2.03 -&gt; OMi 2.21 (Items!P2028, M032) | End A bore not printed by Air-Way (---): D 1.08 used through</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>6505-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6505-24-24</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>6505-24-24</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Male Pipe x Female JIC Swivel Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 1.08 used through</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>6505-20-20</t>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 2.94 -&gt; 3.0 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.21 -&gt; 2.27 | End A bore not printed by Air-Way (---): D 1.31 used through</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>6505-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6505-32-32</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.51554</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>6505-32-32</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Male Pipe x Female JIC Swivel Connector, 2-11 1/2 NPTF x 2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2030 = 2.625 (table had 2.5) | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 3.59 -&gt; 3.44 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.65 -&gt; 2.5 | End A bore not printed by Air-Way (---): D 1.78 used through</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>6505-32-32</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6505_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6505_SW2.xlsx
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="C2" t="n">
         <v>0.50807</v>
@@ -779,25 +779,25 @@
         <v>0.375</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.39</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9225</v>
+        <v>0.8825</v>
       </c>
       <c r="AL2" t="n">
         <v>0.39</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6375</v>
+        <v>0.5975</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9225</v>
+        <v>0.8825</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.095</v>
+        <v>1.015</v>
       </c>
       <c r="AP2" t="n">
         <v>0.88</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2018 = 1.98 (table had 1.9) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2018 = 1.56 (table had 1.48) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2018 = 1.98 (table had 1.9) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2018 = 1.56 (table had 1.48) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.9 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.56) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.9 -&gt; OMi 1.98 (Items!L2018, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.56 (Items!P2018, M032) | End A bore not printed by Air-Way (---): D 0.39 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.9 -&gt; OMi 1.98 (Items!L2018, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.56 (Items!P2018, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.9 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.56 -&gt; Air-Way 1.48 | End A bore not printed by Air-Way (---): D 0.39 used through</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="C3" t="n">
-        <v>0.28868</v>
+        <v>0.25403</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="E3" t="n">
         <v>0.19657</v>
@@ -936,7 +936,7 @@
         <v>0.1845</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AC3" t="n">
         <v>0.145</v>
@@ -957,13 +957,13 @@
         <v>0.21875</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5275</v>
+        <v>0.5175</v>
       </c>
       <c r="AL3" t="n">
         <v>0.17</v>
@@ -972,10 +972,10 @@
         <v>0.4825</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.5275</v>
+        <v>0.5175</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.675</v>
+        <v>0.655</v>
       </c>
       <c r="AP3" t="n">
         <v>0.5600000000000001</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2009 = 1.36 (table had 1.34) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2009 = 1.01 (table had 1) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2009 = 1.36 (table had 1.34) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2009 = 1.01 (table had 1) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.01) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 0.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.34 -&gt; OMi 1.36 (Items!L2009, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1 -&gt; OMi 1.01 (Items!P2009, M032) | End A bore not printed by Air-Way (---): D 0.17 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.34 -&gt; OMi 1.36 (Items!L2009, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1 -&gt; OMi 1.01 (Items!P2009, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.34 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.01 -&gt; Air-Way 1 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 0.5 -&gt; Air-Way 0.44 | End A bore not printed by Air-Way (---): D 0.17 used through</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="C4" t="n">
         <v>0.32332</v>
@@ -1114,7 +1114,7 @@
         <v>0.1845</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AC4" t="n">
         <v>0.145</v>
@@ -1135,25 +1135,25 @@
         <v>0.21875</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7175</v>
+        <v>0.7025</v>
       </c>
       <c r="AL4" t="n">
         <v>0.17</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.4925</v>
+        <v>0.4875</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7175</v>
+        <v>0.7025</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.875</v>
+        <v>0.845</v>
       </c>
       <c r="AP4" t="n">
         <v>0.5600000000000001</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2011 = 1.56 (table had 1.53) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2011 = 1.21 (table had 1.19) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2011 = 1.56 (table had 1.53) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2011 = 1.21 (table had 1.19) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.56) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.53 -&gt; OMi 1.56 (Items!L2011, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.19 -&gt; OMi 1.21 (Items!P2011, M032) | End A bore not printed by Air-Way (---): D 0.17 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.53 -&gt; OMi 1.56 (Items!L2011, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.19 -&gt; OMi 1.21 (Items!P2011, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.56 -&gt; Air-Way 1.53 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.21 -&gt; Air-Way 1.19 | End A bore not printed by Air-Way (---): D 0.17 used through</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="C5" t="n">
         <v>0.32332</v>
@@ -1292,7 +1292,7 @@
         <v>0.218</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AC5" t="n">
         <v>0.175</v>
@@ -1313,25 +1313,25 @@
         <v>0.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
       <c r="AL5" t="n">
         <v>0.23</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.533</v>
+        <v>0.538</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.894</v>
+        <v>0.884</v>
       </c>
       <c r="AP5" t="n">
         <v>0.63</v>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2012 = 1.64 (table had 1.63) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2012 = 1.64 (table had 1.63) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.64) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.63 -&gt; OMi 1.64 (Items!L2012, M031) | End A bore not printed by Air-Way (---): D 0.23 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.63 -&gt; OMi 1.64 (Items!L2012, M031) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.64 -&gt; Air-Way 1.63 | End A bore not printed by Air-Way (---): D 0.23 used through</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="C6" t="n">
         <v>0.32332</v>
@@ -1491,25 +1491,25 @@
         <v>0.28125</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.7275</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="AL6" t="n">
         <v>0.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5725</v>
+        <v>0.5925</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.7275</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.895</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AP6" t="n">
         <v>0.6899999999999999</v>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2013 = 1.68 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2013 = 1.30 (table had 1.34) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2013 = 1.68 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2013 = 1.30 (table had 1.34) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.68 (Items!L2013, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.30 (Items!P2013, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.68 (Items!L2013, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.30 (Items!P2013, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.68 -&gt; Air-Way 1.72 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.3 -&gt; Air-Way 1.34</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="C8" t="n">
         <v>0.43301</v>
@@ -1847,25 +1847,25 @@
         <v>0.28125</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.7075</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="AL8" t="n">
         <v>0.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5525</v>
+        <v>0.5925</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.7075</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.855</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AP8" t="n">
         <v>0.6899999999999999</v>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2015 = 1.64 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2015 = 1.26 (table had 1.34) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2015 = 1.64 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2015 = 1.26 (table had 1.34) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.64) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.64 (Items!L2015, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.26 (Items!P2015, M032) | End A bore not printed by Air-Way (---): D 0.3 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.64 (Items!L2015, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.26 (Items!P2015, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.64 -&gt; Air-Way 1.72 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.34 | End A bore not printed by Air-Way (---): D 0.3 used through</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -1929,10 +1929,10 @@
         <v>1.73</v>
       </c>
       <c r="C9" t="n">
-        <v>0.50518</v>
+        <v>0.46765</v>
       </c>
       <c r="D9" t="n">
-        <v>0.875</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>0.32823</v>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2016 Hex Flat = 0.875 (table had 0.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2016 Hex Flat = 0.875 (table had 0.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; CHEX@HEX: Air-Way 0.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | End A bore not printed by Air-Way (---): D 0.39 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.81 | End A bore not printed by Air-Way (---): D 0.39 used through</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="C10" t="n">
         <v>0.50807</v>
@@ -2182,7 +2182,7 @@
         <v>0.246</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AC10" t="n">
         <v>0.215</v>
@@ -2203,25 +2203,25 @@
         <v>0.28125</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.53</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.9225</v>
+        <v>0.9125</v>
       </c>
       <c r="AL10" t="n">
         <v>0.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5875</v>
+        <v>0.5675</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.9225</v>
+        <v>0.9125</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.095</v>
+        <v>1.075</v>
       </c>
       <c r="AP10" t="n">
         <v>0.6899999999999999</v>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2017 = 1.88 (table had 1.86) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2017 = 1.51 (table had 1.48) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2017 = 1.88 (table had 1.86) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2017 = 1.51 (table had 1.48) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.86 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.88) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.51) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.86 -&gt; OMi 1.88 (Items!L2017, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.51 (Items!P2017, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.86 -&gt; OMi 1.88 (Items!L2017, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.51 (Items!P2017, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.88 -&gt; Air-Way 1.86 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.51 -&gt; Air-Way 1.48</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="C11" t="n">
-        <v>0.57735</v>
+        <v>0.54271</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.40779</v>
@@ -2381,25 +2381,25 @@
         <v>0.4375</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.48</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.9325</v>
+        <v>1.0225</v>
       </c>
       <c r="AL11" t="n">
         <v>0.48</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.6675</v>
+        <v>0.7575</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.9325</v>
+        <v>1.0225</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.115</v>
+        <v>1.295</v>
       </c>
       <c r="AP11" t="n">
         <v>1</v>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2019 = 2.10 (table had 2.28) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2019 = 1.60 (table had 1.78) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2019 = 2.10 (table had 2.28) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2019 = 1.60 (table had 1.78) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.28 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.78 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.28 -&gt; OMi 2.10 (Items!L2019, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.78 -&gt; OMi 1.60 (Items!P2019, M032) | End A bore not printed by Air-Way (---): D 0.48 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.28 -&gt; OMi 2.10 (Items!L2019, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.78 -&gt; OMi 1.60 (Items!P2019, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.1 -&gt; Air-Way 2.28 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.6 -&gt; Air-Way 1.78 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94 | End A bore not printed by Air-Way (---): D 0.48 used through</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="C12" t="n">
-        <v>0.57735</v>
+        <v>0.65241</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="E12" t="n">
         <v>0.40779</v>
@@ -2559,25 +2559,25 @@
         <v>0.53125</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.53</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.9005</v>
+        <v>0.9605</v>
       </c>
       <c r="AL12" t="n">
         <v>0.61</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.6795</v>
+        <v>0.7395</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.9005</v>
+        <v>0.9605</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.051</v>
+        <v>1.171</v>
       </c>
       <c r="AP12" t="n">
         <v>1.25</v>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2020 = 2.14 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2020 = 1.58 (table had 1.7) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2020 = 2.14 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2020 = 1.58 (table had 1.7) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.26 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.14 (Items!L2020, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.58 (Items!P2020, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.14 (Items!L2020, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.58 (Items!P2020, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.14 -&gt; Air-Way 2.26 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.7 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 1 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="C14" t="n">
         <v>0.65241</v>
@@ -2894,7 +2894,7 @@
         <v>0.394</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AC14" t="n">
         <v>0.3375</v>
@@ -2915,25 +2915,25 @@
         <v>0.4375</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.72</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.9875</v>
+        <v>0.9925</v>
       </c>
       <c r="AL14" t="n">
         <v>0.48</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.7125</v>
+        <v>0.7275</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.9875</v>
+        <v>0.9925</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.225</v>
+        <v>1.235</v>
       </c>
       <c r="AP14" t="n">
         <v>1</v>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2022 = 2.21 (table had 2.22) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2022 = 1.70 (table had 1.72) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2022 = 2.21 (table had 2.22) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2022 = 1.70 (table had 1.72) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.22 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.7) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.22 -&gt; OMi 2.21 (Items!L2022, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.72 -&gt; OMi 1.70 (Items!P2022, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.22 -&gt; OMi 2.21 (Items!L2022, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.72 -&gt; OMi 1.70 (Items!P2022, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.21 -&gt; Air-Way 2.22 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.7 -&gt; Air-Way 1.72</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="C15" t="n">
         <v>0.65241</v>
@@ -3093,25 +3093,25 @@
         <v>0.53125</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.61</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.9705</v>
+        <v>0.9605</v>
       </c>
       <c r="AL15" t="n">
         <v>0.61</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.7395</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.9705</v>
+        <v>0.9605</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.191</v>
+        <v>1.171</v>
       </c>
       <c r="AP15" t="n">
         <v>1.25</v>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2023 = 2.28 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2023 = 1.72 (table had 1.7) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2023 = 2.28 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2023 = 1.72 (table had 1.7) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.26 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.28 (Items!L2023, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.72 (Items!P2023, M032) | End A bore not printed by Air-Way (---): D 0.61 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.28 (Items!L2023, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.72 (Items!P2023, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.28 -&gt; Air-Way 2.26 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.7 | End A bore not printed by Air-Way (---): D 0.61 used through</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="C16" t="n">
         <v>0.79674</v>
@@ -3271,25 +3271,25 @@
         <v>0.65625</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AJ16" t="n">
         <v>0.72</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.9775</v>
+        <v>0.9675</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.719</v>
+        <v>0.84</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.8125</v>
+        <v>0.8025</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.9775</v>
+        <v>0.9675</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.205</v>
+        <v>1.185</v>
       </c>
       <c r="AP16" t="n">
         <v>1.5</v>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2024 = 2.38 (table had 2.36) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2024 = 1.79 (table had 1.77) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2024 = 2.38 (table had 2.36) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2024 = 1.79 (table had 1.77) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.38) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.77 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.79) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.84 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.719) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.36 -&gt; OMi 2.38 (Items!L2024, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.77 -&gt; OMi 1.79 (Items!P2024, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.36 -&gt; OMi 2.38 (Items!L2024, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.77 -&gt; OMi 1.79 (Items!P2024, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.38 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.79 -&gt; Air-Way 1.77 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.719 -&gt; Air-Way 0.84</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="C20" t="n">
         <v>0.97572</v>
@@ -3978,25 +3978,25 @@
         <v>0.8125</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.08</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.275</v>
+        <v>1.185</v>
       </c>
       <c r="AL20" t="n">
         <v>1.08</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.845</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.275</v>
+        <v>1.185</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AP20" t="n">
         <v>2</v>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2028 = 2.84 (table had 2.66) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2028 = 2.21 (table had 2.03) [user 2026-10-18 A19] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2028 = 2.84 (table had 2.66) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2028 = 2.21 (table had 2.03) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.66 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.84) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.66 -&gt; OMi 2.84 (Items!L2028, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 2.03 -&gt; OMi 2.21 (Items!P2028, M032) | End A bore not printed by Air-Way (---): D 1.08 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.66 -&gt; OMi 2.84 (Items!L2028, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 2.03 -&gt; OMi 2.21 (Items!P2028, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.84 -&gt; Air-Way 2.66 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 2.21 -&gt; Air-Way 2.03 | End A bore not printed by Air-Way (---): D 1.08 used through</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="C21" t="n">
         <v>1.1547</v>
@@ -4156,25 +4156,25 @@
         <v>0.9375</v>
       </c>
       <c r="AI21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.31</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.295</v>
+        <v>1.265</v>
       </c>
       <c r="AL21" t="n">
         <v>1.31</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.975</v>
+        <v>0.945</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.295</v>
+        <v>1.265</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AP21" t="n">
         <v>2.25</v>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: Air-Way 2.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 2.21 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 2.94 -&gt; 3.0 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.21 -&gt; 2.27 | End A bore not printed by Air-Way (---): D 1.31 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 2.94 -&gt; 3.0 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.21 -&gt; 2.27 | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 3 -&gt; Air-Way 2.94 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.21 | End A bore not printed by Air-Way (---): D 1.31 used through</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="C22" t="n">
-        <v>1.51554</v>
+        <v>1.44338</v>
       </c>
       <c r="D22" t="n">
-        <v>2.625</v>
+        <v>2.5</v>
       </c>
       <c r="E22" t="n">
         <v>1.16929</v>
@@ -4334,25 +4334,25 @@
         <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.78</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>1.475</v>
       </c>
       <c r="AL22" t="n">
         <v>1.78</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.1</v>
+        <v>1.175</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.4</v>
+        <v>1.475</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AP22" t="n">
         <v>2.88</v>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: Air-Way 3.59 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.44) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 2.65 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 2.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.625) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); L15 = pipe tip to the nut face, L16 = pipe tip to the seat; body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1 (pipe side, where Air-Way prints one; D where it prints ---) / D (swivel side) stepped at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2030 = 2.625 (table had 2.5) | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 3.59 -&gt; 3.44 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.65 -&gt; 2.5 | End A bore not printed by Air-Way (---): D 1.78 used through</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2030 = 2.625 (table had 2.5) | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 3.59 -&gt; 3.44 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.65 -&gt; 2.5 | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 3.44 -&gt; Air-Way 3.59 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 2.5 -&gt; Air-Way 2.65 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 2.625 -&gt; Air-Way 2.5 | End A bore not printed by Air-Way (---): D 1.78 used through</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
